--- a/Matriz_BR_UR_FR_NFR.xlsx
+++ b/Matriz_BR_UR_FR_NFR.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cb58a5af5ad1fd41/Desktop/sexto/ingenieria de requisitos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cb58a5af5ad1fd41/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B225ADE-41C5-4263-825D-BA53A2C1D18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{04EAC6EB-69DB-45DF-B5D4-06A6834A431C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D21A7160-1D45-4AC6-88E9-CFB69D31C72A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,15 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="114">
-  <si>
-    <t>Proyecto: StoreBrand Auto — Storebrand Bank ASA  |  UTPL — Ingeniería de Requisitos  |  Fecha: 06/05/2026</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="116">
   <si>
     <t>ID BR</t>
   </si>
   <si>
-    <t>Objetivo de Negocio (Business Requirement)</t>
+    <t>Objetivo de Negocio (SMART)</t>
   </si>
   <si>
     <t>Métrica / KPI</t>
@@ -40,7 +37,7 @@
     <t>ID UR</t>
   </si>
   <si>
-    <t>Necesidad de Usuario (User Requirement)</t>
+    <t>Necesidad de Usuario</t>
   </si>
   <si>
     <t>Stakeholder</t>
@@ -64,13 +61,13 @@
     <t>Requisito No Funcional</t>
   </si>
   <si>
-    <t>Categoría</t>
+    <t>Categoría ISO 25010</t>
   </si>
   <si>
     <t>BN-01</t>
   </si>
   <si>
-    <t>Reducir el tiempo de procesamiento de solicitudes de productos bancarios en un 50% mediante automatización de procesos de validación y aprobación.</t>
+    <t>Reducir el tiempo de procesamiento de solicitudes de productos bancarios en un 50% mediante la automatización de procesos de validación y aprobación.</t>
   </si>
   <si>
     <t>Tiempo promedio de respuesta ≤ 1 hora para solicitudes estándar</t>
@@ -82,13 +79,40 @@
     <t>UR-01</t>
   </si>
   <si>
-    <t>Solicitar productos financieros (préstamos, tarjetas, hipotecas) de forma rápida y con respuesta oportuna.</t>
-  </si>
-  <si>
-    <t>Cliente del banco</t>
-  </si>
-  <si>
-    <t>FR-01</t>
+    <t>Acceder a una plataforma digital para solicitar préstamos, hipotecas, tarjetas y productos de ahorro. (NEC-01)</t>
+  </si>
+  <si>
+    <t>Cliente del banco (USR-03)</t>
+  </si>
+  <si>
+    <t>RF-001</t>
+  </si>
+  <si>
+    <t>El sistema deberá permitir que los usuarios autorizados inicien sesión mediante credenciales válidas.</t>
+  </si>
+  <si>
+    <t>Todos los usuarios</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>RNF-DES-001</t>
+  </si>
+  <si>
+    <t>El sistema deberá responder a consultas simples en un máximo de 3 segundos.</t>
+  </si>
+  <si>
+    <t>Eficiencia de desempeño</t>
+  </si>
+  <si>
+    <t>UR-02</t>
+  </si>
+  <si>
+    <t>Registrar solicitudes de productos financieros de forma rápida y recibir confirmación inmediata. (NEC-01)</t>
+  </si>
+  <si>
+    <t>RF-003</t>
   </si>
   <si>
     <t>El sistema deberá permitir registrar solicitudes de productos financieros.</t>
@@ -97,37 +121,34 @@
     <t>Cliente</t>
   </si>
   <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>NFR-01</t>
-  </si>
-  <si>
-    <t>El sistema deberá responder a consultas simples en un máximo de 3 segundos.</t>
-  </si>
-  <si>
-    <t>Rendimiento</t>
-  </si>
-  <si>
-    <t>UR-02</t>
-  </si>
-  <si>
-    <t>Recibir notificaciones automáticas sobre el estado de sus solicitudes bancarias.</t>
-  </si>
-  <si>
-    <t>FR-02</t>
-  </si>
-  <si>
-    <t>El sistema deberá mostrar opciones y funcionalidades de acuerdo con el rol asignado al usuario.</t>
-  </si>
-  <si>
-    <t>Todos los usuarios</t>
-  </si>
-  <si>
-    <t>NFR-02</t>
-  </si>
-  <si>
-    <t>El sistema deberá soportar al menos 500 usuarios concurrentes sin degradación significativa del servicio.</t>
+    <t>RNF-DES-002</t>
+  </si>
+  <si>
+    <t>El sistema deberá soportar al menos 200 usuarios concurrentes sin degradación significativa del servicio.</t>
+  </si>
+  <si>
+    <t>UR-03</t>
+  </si>
+  <si>
+    <t>Cargar y validar documentos asociados a solicitudes sin procesos manuales repetitivos. (NEC-01)</t>
+  </si>
+  <si>
+    <t>Cliente / Analista (USR-02, USR-03)</t>
+  </si>
+  <si>
+    <t>RF-005</t>
+  </si>
+  <si>
+    <t>El sistema deberá permitir cargar, visualizar y validar documentos asociados a una solicitud.</t>
+  </si>
+  <si>
+    <t>Cliente, Analista Bancario</t>
+  </si>
+  <si>
+    <t>RNF-DES-003</t>
+  </si>
+  <si>
+    <t>El sistema deberá procesar al menos 100 transacciones por minuto relacionadas con solicitudes y validaciones.</t>
   </si>
   <si>
     <t>BN-02</t>
@@ -142,16 +163,16 @@
     <t>8 meses post-lanzamiento</t>
   </si>
   <si>
-    <t>UR-03</t>
-  </si>
-  <si>
-    <t>Consultar y dar seguimiento al estado de solicitudes bancarias sin intervención manual.</t>
-  </si>
-  <si>
-    <t>Analista / Back Office</t>
-  </si>
-  <si>
-    <t>FR-03</t>
+    <t>UR-04</t>
+  </si>
+  <si>
+    <t>Automatizar tareas repetitivas de validación y gestión de solicitudes para concentrarse en casos críticos. (NEC-02)</t>
+  </si>
+  <si>
+    <t>Analista bancario (USR-02)</t>
+  </si>
+  <si>
+    <t>RF-004</t>
   </si>
   <si>
     <t>El sistema deberá permitir consultar, actualizar y dar seguimiento a las solicitudes registradas.</t>
@@ -160,7 +181,85 @@
     <t>Analista Bancario, Supervisor</t>
   </si>
   <si>
-    <t>NFR-03</t>
+    <t>RNF-AF-001</t>
+  </si>
+  <si>
+    <t>El sistema deberá permitir ejecutar completamente el flujo de registro, validación, aprobación y seguimiento sin herramientas externas.</t>
+  </si>
+  <si>
+    <t>Adecuación funcional</t>
+  </si>
+  <si>
+    <t>UR-05</t>
+  </si>
+  <si>
+    <t>Aprobar, rechazar o solicitar correcciones sobre solicitudes con intervención humana en casos de alto riesgo. (NEC-02)</t>
+  </si>
+  <si>
+    <t>Analista / Supervisor (USR-02, USR-04)</t>
+  </si>
+  <si>
+    <t>RF-006</t>
+  </si>
+  <si>
+    <t>El sistema deberá permitir aprobar, rechazar o solicitar correcciones sobre una solicitud bancaria.</t>
+  </si>
+  <si>
+    <t>RNF-AF-003</t>
+  </si>
+  <si>
+    <t>El sistema deberá garantizar que cada solicitud bancaria mantenga trazabilidad completa durante todo su ciclo de vida.</t>
+  </si>
+  <si>
+    <t>UR-06</t>
+  </si>
+  <si>
+    <t>Controlar el acceso a funcionalidades e información según el rol asignado. (NEC-02 / NEC-03)</t>
+  </si>
+  <si>
+    <t>RF-002</t>
+  </si>
+  <si>
+    <t>El sistema deberá controlar el acceso a funcionalidades, información y operaciones de acuerdo con el rol asignado.</t>
+  </si>
+  <si>
+    <t>RNF-SEG-002</t>
+  </si>
+  <si>
+    <t>El sistema deberá aplicar autorización basada en roles.</t>
+  </si>
+  <si>
+    <t>Seguridad</t>
+  </si>
+  <si>
+    <t>BN-03</t>
+  </si>
+  <si>
+    <t>Incrementar en un 30% la satisfacción del cliente mediante la mejora en la velocidad y calidad del servicio en la gestión de solicitudes bancarias.</t>
+  </si>
+  <si>
+    <t>Nivel de satisfacción del cliente ≥ 90% en encuestas de servicio</t>
+  </si>
+  <si>
+    <t>12 meses post-lanzamiento</t>
+  </si>
+  <si>
+    <t>UR-07</t>
+  </si>
+  <si>
+    <t>Recibir notificaciones oportunas sobre el estado de solicitudes y trámites bancarios. (NEC-05)</t>
+  </si>
+  <si>
+    <t>RF-010</t>
+  </si>
+  <si>
+    <t>El sistema deberá generar y mostrar notificaciones relacionadas con cambios de estado, aprobaciones o incidencias.</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>RNF-FIA-001</t>
   </si>
   <si>
     <t>El sistema deberá estar disponible al menos el 99% del tiempo operativo.</t>
@@ -169,181 +268,88 @@
     <t>Fiabilidad</t>
   </si>
   <si>
-    <t>UR-04</t>
-  </si>
-  <si>
-    <t>Cargar, visualizar y validar documentos de clientes de forma automatizada.</t>
-  </si>
-  <si>
-    <t>FR-04</t>
-  </si>
-  <si>
-    <t>El sistema deberá permitir cargar, visualizar y validar documentos asociados a una solicitud.</t>
-  </si>
-  <si>
-    <t>Cliente, Analista Bancario</t>
-  </si>
-  <si>
-    <t>NFR-04</t>
+    <t>UR-08</t>
+  </si>
+  <si>
+    <t>Consultar el historial completo y trazabilidad de acciones sobre solicitudes. (NEC-04)</t>
+  </si>
+  <si>
+    <t>Supervisor / Analista (USR-02, USR-04)</t>
+  </si>
+  <si>
+    <t>RF-009</t>
+  </si>
+  <si>
+    <t>El sistema deberá registrar y mostrar el historial completo de acciones realizadas sobre una solicitud.</t>
+  </si>
+  <si>
+    <t>Analista, Supervisor, Administrador</t>
+  </si>
+  <si>
+    <t>RNF-FIA-002</t>
   </si>
   <si>
     <t>El sistema deberá recuperarse ante fallos en un máximo de 15 minutos.</t>
   </si>
   <si>
-    <t>UR-05</t>
-  </si>
-  <si>
-    <t>Aprobar, rechazar o solicitar correcciones sobre solicitudes bancarias con intervención humana controlada.</t>
-  </si>
-  <si>
-    <t>Analista / Control de riesgos</t>
-  </si>
-  <si>
-    <t>FR-05</t>
-  </si>
-  <si>
-    <t>El sistema deberá permitir aprobar, rechazar o solicitar correcciones sobre una solicitud bancaria.</t>
-  </si>
-  <si>
-    <t>NFR-05</t>
-  </si>
-  <si>
-    <t>El sistema deberá registrar errores críticos para diagnóstico posterior.</t>
-  </si>
-  <si>
-    <t>BN-03</t>
-  </si>
-  <si>
-    <t>Incrementar en un 30% la satisfacción del cliente mediante la mejora en la velocidad y calidad del servicio en la gestión de solicitudes bancarias.</t>
-  </si>
-  <si>
-    <t>Nivel de satisfacción del cliente ≥ 90% en encuestas de servicio</t>
-  </si>
-  <si>
-    <t>12 meses post-lanzamiento</t>
-  </si>
-  <si>
-    <t>UR-06</t>
-  </si>
-  <si>
-    <t>Autenticarse de forma segura y acceder al sistema con credenciales propias.</t>
-  </si>
-  <si>
-    <t>FR-06</t>
-  </si>
-  <si>
-    <t>El sistema deberá permitir que los usuarios accedan mediante credenciales válidas.</t>
-  </si>
-  <si>
-    <t>NFR-06</t>
+    <t>BN-04</t>
+  </si>
+  <si>
+    <t>Garantizar trazabilidad, control y continuidad operativa con disponibilidad ≥ 99% en todos los procesos automatizados.</t>
+  </si>
+  <si>
+    <t>Disponibilidad ≥ 99%; 100% de solicitudes con trazabilidad completa registrada</t>
+  </si>
+  <si>
+    <t>Continuo post-lanzamiento</t>
+  </si>
+  <si>
+    <t>UR-09</t>
+  </si>
+  <si>
+    <t>Supervisar el funcionamiento de automatizaciones, gestionar usuarios y garantizar continuidad operativa. (NEC-03)</t>
+  </si>
+  <si>
+    <t>Administrador (USR-01)</t>
+  </si>
+  <si>
+    <t>RF-007</t>
+  </si>
+  <si>
+    <t>El sistema deberá mostrar indicadores, estados y alertas relacionados con los procesos automatizados.</t>
+  </si>
+  <si>
+    <t>Supervisor, Administrador</t>
+  </si>
+  <si>
+    <t>RNF-SEG-001</t>
   </si>
   <si>
     <t>El sistema deberá autenticar usuarios antes de permitir acceso a funciones protegidas.</t>
   </si>
   <si>
-    <t>Seguridad</t>
-  </si>
-  <si>
-    <t>UR-07</t>
-  </si>
-  <si>
-    <t>Recibir notificaciones automáticas al banco sobre aprobaciones, rechazos e incidencias.</t>
-  </si>
-  <si>
-    <t>FR-07</t>
-  </si>
-  <si>
-    <t>El sistema deberá generar y mostrar notificaciones relacionadas con cambios de estado, aprobaciones o incidencias.</t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>NFR-07</t>
-  </si>
-  <si>
-    <t>El sistema deberá aplicar autorización basada en roles.</t>
-  </si>
-  <si>
-    <t>BN-04</t>
-  </si>
-  <si>
-    <t>Garantizar trazabilidad, control y continuidad operativa ≥ 99% en todos los procesos automatizados del banco.</t>
-  </si>
-  <si>
-    <t>Disponibilidad ≥ 99%; reportes automáticos de trazabilidad 100% generados</t>
-  </si>
-  <si>
-    <t>Continuo post-lanzamiento</t>
-  </si>
-  <si>
-    <t>UR-08</t>
-  </si>
-  <si>
-    <t>Monitorear indicadores operativos, estados y alertas de los procesos automatizados.</t>
-  </si>
-  <si>
-    <t>Supervisor / Gerente de Operaciones</t>
-  </si>
-  <si>
-    <t>FR-08</t>
-  </si>
-  <si>
-    <t>El sistema deberá mostrar indicadores, estados y alertas relacionados con los procesos automatizados.</t>
-  </si>
-  <si>
-    <t>Supervisor, Administrador</t>
-  </si>
-  <si>
-    <t>NFR-08</t>
-  </si>
-  <si>
-    <t>El sistema deberá cifrar información sensible en tránsito (HTTPS/TLS).</t>
-  </si>
-  <si>
-    <t>UR-09</t>
-  </si>
-  <si>
-    <t>Consultar el historial completo y trazabilidad de acciones realizadas sobre una solicitud.</t>
-  </si>
-  <si>
-    <t>Analista / Auditor</t>
-  </si>
-  <si>
-    <t>FR-09</t>
-  </si>
-  <si>
-    <t>El sistema deberá registrar y mostrar el historial completo de acciones realizadas sobre una solicitud.</t>
-  </si>
-  <si>
-    <t>Analista Bancario, Supervisor, Admin.</t>
-  </si>
-  <si>
-    <t>NFR-09</t>
-  </si>
-  <si>
-    <t>El sistema deberá registrar eventos de seguridad (accesos, intentos fallidos, cambios críticos).</t>
-  </si>
-  <si>
     <t>UR-10</t>
   </si>
   <si>
-    <t>Administrar usuarios, roles y permisos del sistema de forma centralizada.</t>
+    <t>Dar seguimiento a solicitudes, validar decisiones críticas y monitorear indicadores operativos. (NEC-04)</t>
+  </si>
+  <si>
+    <t>Supervisor (USR-04)</t>
+  </si>
+  <si>
+    <t>RF-008</t>
+  </si>
+  <si>
+    <t>El sistema deberá permitir crear, modificar y administrar usuarios, roles y permisos.</t>
   </si>
   <si>
     <t>Administrador</t>
   </si>
   <si>
-    <t>FR-10</t>
-  </si>
-  <si>
-    <t>El sistema deberá permitir crear, modificar y administrar usuarios, roles y permisos.</t>
-  </si>
-  <si>
-    <t>NFR-10</t>
-  </si>
-  <si>
-    <t>El sistema deberá soportar el crecimiento hasta 1.000 usuarios concurrentes sin rediseño mayor.</t>
+    <t>RNF-ESC-001</t>
+  </si>
+  <si>
+    <t>El sistema deberá soportar el crecimiento hasta 1.000 usuarios concurrentes sin rediseño mayor de la arquitectura.</t>
   </si>
   <si>
     <t>Escalabilidad</t>
@@ -352,13 +358,13 @@
     <t xml:space="preserve">BR — BUSINESS REQUIREMENTS </t>
   </si>
   <si>
-    <t xml:space="preserve">UR — USER REQUIREMENTS </t>
+    <t xml:space="preserve">UR — USER REQUIREMENTS  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR — FUNCTIONAL REQUIREMENTS </t>
   </si>
   <si>
     <t xml:space="preserve">NFR — NON-FUNCTIONAL REQUIREMENTS </t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR — FUNCTIONAL REQUIREMENTS </t>
   </si>
   <si>
     <t>Business Requirements → User Requirements → Functional Requirements → Non-Functional Requirements</t>
@@ -553,7 +559,7 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -562,7 +568,7 @@
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -571,7 +577,7 @@
     <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -592,7 +598,7 @@
     <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -601,7 +607,7 @@
     <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -610,7 +616,7 @@
     <xf numFmtId="0" fontId="6" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -938,23 +944,24 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="9" width="28" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="12" width="9" customWidth="1"/>
-    <col min="13" max="13" width="28" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="11" max="11" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
+    <col min="13" max="13" width="30" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="37" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
@@ -970,10 +977,8 @@
       <c r="M1" s="32"/>
       <c r="N1" s="32"/>
     </row>
-    <row r="2" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
-        <v>0</v>
-      </c>
+    <row r="2" spans="1:14" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="34"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -990,260 +995,260 @@
     </row>
     <row r="3" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B3" s="32"/>
       <c r="C3" s="32"/>
       <c r="D3" s="32"/>
       <c r="E3" s="35" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F3" s="32"/>
       <c r="G3" s="32"/>
       <c r="H3" s="31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I3" s="32"/>
       <c r="J3" s="32"/>
       <c r="K3" s="32"/>
       <c r="L3" s="36" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M3" s="32"/>
       <c r="N3" s="32"/>
     </row>
     <row r="4" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="M4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="N4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="N4" s="4" t="s">
+    </row>
+    <row r="5" spans="1:14" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
+      <c r="B5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="17" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="5" spans="1:14" ht="88.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+    <row r="6" spans="1:14" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="10" t="s">
+      <c r="E6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="14" t="s">
+      <c r="H6" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" s="16" t="s">
+      <c r="L6" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="N6" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="N5" s="17" t="s">
-        <v>28</v>
-      </c>
     </row>
-    <row r="6" spans="1:14" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+    <row r="7" spans="1:14" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="M6" s="16" t="s">
+      <c r="E7" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="N6" s="17" t="s">
-        <v>28</v>
+      <c r="F7" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" s="25" t="s">
+    <row r="8" spans="1:14" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="I7" s="26" t="s">
+      <c r="B8" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="J7" s="27" t="s">
+      <c r="C8" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="K7" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="L7" s="28" t="s">
+      <c r="D8" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="M7" s="29" t="s">
+      <c r="E8" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="N7" s="30" t="s">
+      <c r="F8" s="23" t="s">
         <v>48</v>
       </c>
+      <c r="G8" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="K8" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="M8" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="N8" s="30" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="8" spans="1:14" ht="76.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="I8" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="J8" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="K8" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="L8" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="M8" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="N8" s="30" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="92.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E9" s="22" t="s">
         <v>56</v>
@@ -1261,10 +1266,10 @@
         <v>60</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="K9" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L9" s="28" t="s">
         <v>61</v>
@@ -1273,65 +1278,65 @@
         <v>62</v>
       </c>
       <c r="N9" s="30" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:14" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="F10" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="G10" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="I10" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="J10" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="M10" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="G10" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="H10" s="12" t="s">
+      <c r="N10" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="I10" s="13" t="s">
+    </row>
+    <row r="11" spans="1:14" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="J10" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="L10" s="15" t="s">
+      <c r="B11" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="M10" s="16" t="s">
+      <c r="C11" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="N10" s="17" t="s">
+      <c r="D11" s="8" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>74</v>
@@ -1340,7 +1345,7 @@
         <v>75</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H11" s="12" t="s">
         <v>76</v>
@@ -1349,7 +1354,7 @@
         <v>77</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="K11" s="12" t="s">
         <v>78</v>
@@ -1361,139 +1366,139 @@
         <v>80</v>
       </c>
       <c r="N11" s="17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>73</v>
       </c>
+      <c r="E12" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
-    <row r="12" spans="1:14" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="F12" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="G12" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="H12" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="I12" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="J12" s="27" t="s">
+    <row r="13" spans="1:14" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="K12" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="L12" s="28" t="s">
+      <c r="B13" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="M12" s="29" t="s">
+      <c r="C13" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="N12" s="30" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>83</v>
-      </c>
       <c r="D13" s="21" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H13" s="25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I13" s="26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K13" s="25" t="s">
         <v>78</v>
       </c>
       <c r="L13" s="28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M13" s="29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N13" s="30" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="67.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H14" s="25" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I14" s="26" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J14" s="27" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K14" s="25" t="s">
         <v>78</v>
       </c>
       <c r="L14" s="28" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M14" s="29" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N14" s="30" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/Matriz_BR_UR_FR_NFR.xlsx
+++ b/Matriz_BR_UR_FR_NFR.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cb58a5af5ad1fd41/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Roble\OneDrive\Desktop\Sexto Ciclo\Ingenieria-Requisitos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{04EAC6EB-69DB-45DF-B5D4-06A6834A431C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D21A7160-1D45-4AC6-88E9-CFB69D31C72A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F173FD-5107-4045-BC27-EC6C6DE720CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Matriz BR-UR-FR-NFR" sheetId="1" r:id="rId1"/>
@@ -619,10 +619,13 @@
     <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -633,9 +636,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -941,7 +941,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -959,8 +959,8 @@
     <col min="14" max="14" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:14" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
         <v>115</v>
       </c>
       <c r="B1" s="32"/>
@@ -977,8 +977,8 @@
       <c r="M1" s="32"/>
       <c r="N1" s="32"/>
     </row>
-    <row r="2" spans="1:14" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="34"/>
+    <row r="2" spans="1:14" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="35"/>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -993,31 +993,31 @@
       <c r="M2" s="32"/>
       <c r="N2" s="32"/>
     </row>
-    <row r="3" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="33" t="s">
+    <row r="3" spans="1:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="34" t="s">
         <v>111</v>
       </c>
       <c r="B3" s="32"/>
       <c r="C3" s="32"/>
       <c r="D3" s="32"/>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="36" t="s">
         <v>112</v>
       </c>
       <c r="F3" s="32"/>
       <c r="G3" s="32"/>
-      <c r="H3" s="31" t="s">
+      <c r="H3" s="33" t="s">
         <v>113</v>
       </c>
       <c r="I3" s="32"/>
       <c r="J3" s="32"/>
       <c r="K3" s="32"/>
-      <c r="L3" s="36" t="s">
+      <c r="L3" s="37" t="s">
         <v>114</v>
       </c>
       <c r="M3" s="32"/>
       <c r="N3" s="32"/>
     </row>
-    <row r="4" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1061,7 +1061,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
@@ -1105,7 +1105,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>14</v>
       </c>
@@ -1149,7 +1149,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
         <v>43</v>
       </c>
@@ -1237,7 +1237,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>43</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
         <v>43</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>70</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>70</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="52.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>90</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="52.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
         <v>90</v>
       </c>
